--- a/rag/eval/results_original120/statistical_tests_original120.xlsx
+++ b/rag/eval/results_original120/statistical_tests_original120.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Table3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
         <v>0.0638</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00242</v>
+        <v>0.00255</v>
       </c>
     </row>
     <row r="3">
@@ -744,22 +744,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.77e-05</v>
+        <v>3.4e-05</v>
       </c>
       <c r="F8" t="n">
         <v>0.851</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="H8" t="n">
         <v>0.114</v>
       </c>
       <c r="I8" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000323</v>
+        <v>0.000291</v>
       </c>
     </row>
     <row r="9">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.000775</v>
+        <v>0.000773</v>
       </c>
       <c r="F9" t="n">
         <v>0.851</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="H9" t="n">
         <v>0.114</v>
       </c>
       <c r="I9" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="J9" t="n">
         <v>0.00404</v>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.859999999999999e-06</v>
+        <v>7.02e-06</v>
       </c>
       <c r="F10" t="n">
         <v>0.851</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H10" t="n">
         <v>0.114</v>
@@ -839,7 +839,7 @@
         <v>0.142</v>
       </c>
       <c r="J10" t="n">
-        <v>9.43e-05</v>
+        <v>8.42e-05</v>
       </c>
     </row>
     <row r="11">
@@ -870,7 +870,7 @@
         <v>0.851</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>0.114</v>
@@ -1144,13 +1144,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.293</v>
+        <v>0.343</v>
       </c>
       <c r="F18" t="n">
         <v>0.799</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782</v>
+        <v>0.784</v>
       </c>
       <c r="H18" t="n">
         <v>0.163</v>
@@ -1159,7 +1159,7 @@
         <v>0.132</v>
       </c>
       <c r="J18" t="n">
-        <v>0.366</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="19">
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.255</v>
+        <v>0.319</v>
       </c>
       <c r="F19" t="n">
         <v>0.799</v>
       </c>
       <c r="G19" t="n">
-        <v>0.782</v>
+        <v>0.784</v>
       </c>
       <c r="H19" t="n">
         <v>0.163</v>
@@ -1199,7 +1199,7 @@
         <v>0.132</v>
       </c>
       <c r="J19" t="n">
-        <v>0.306</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="20">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F20" t="n">
         <v>0.799</v>
       </c>
       <c r="G20" t="n">
-        <v>0.799</v>
+        <v>0.801</v>
       </c>
       <c r="H20" t="n">
         <v>0.163</v>
@@ -1239,7 +1239,7 @@
         <v>0.123</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.826</v>
+        <v>0.706</v>
       </c>
       <c r="F21" t="n">
         <v>0.799</v>
       </c>
       <c r="G21" t="n">
-        <v>0.799</v>
+        <v>0.801</v>
       </c>
       <c r="H21" t="n">
         <v>0.163</v>
@@ -1279,7 +1279,7 @@
         <v>0.123</v>
       </c>
       <c r="J21" t="n">
-        <v>0.869</v>
+        <v>0.743</v>
       </c>
     </row>
     <row r="22">
@@ -1479,7 +1479,7 @@
         <v>0.112</v>
       </c>
       <c r="J26" t="n">
-        <v>0.506</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="27">
@@ -1519,7 +1519,7 @@
         <v>0.112</v>
       </c>
       <c r="J27" t="n">
-        <v>0.298</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="28">
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.00216</v>
+        <v>0.00217</v>
       </c>
       <c r="F28" t="n">
         <v>0.804</v>
       </c>
       <c r="G28" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="H28" t="n">
         <v>0.129</v>
@@ -1559,7 +1559,7 @@
         <v>0.142</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00648</v>
+        <v>0.00651</v>
       </c>
     </row>
     <row r="29">
@@ -1590,7 +1590,7 @@
         <v>0.804</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="H29" t="n">
         <v>0.129</v>
@@ -1630,7 +1630,7 @@
         <v>0.804</v>
       </c>
       <c r="G30" t="n">
-        <v>0.714</v>
+        <v>0.715</v>
       </c>
       <c r="H30" t="n">
         <v>0.129</v>
@@ -1670,7 +1670,7 @@
         <v>0.804</v>
       </c>
       <c r="G31" t="n">
-        <v>0.714</v>
+        <v>0.715</v>
       </c>
       <c r="H31" t="n">
         <v>0.129</v>
@@ -1759,7 +1759,7 @@
         <v>0.064</v>
       </c>
       <c r="J33" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
     </row>
     <row r="34">
@@ -1799,7 +1799,7 @@
         <v>0.174</v>
       </c>
       <c r="J34" t="n">
-        <v>0.398</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="35">
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.43e-08</v>
+        <v>4.45e-08</v>
       </c>
       <c r="F38" t="n">
         <v>0.87</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H38" t="n">
         <v>0.199</v>
       </c>
       <c r="I38" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="J38" t="n">
-        <v>1.33e-06</v>
+        <v>1.34e-06</v>
       </c>
     </row>
     <row r="39">
@@ -1990,13 +1990,13 @@
         <v>0.87</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H39" t="n">
         <v>0.199</v>
       </c>
       <c r="I39" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="J39" t="n">
         <v>0.000458</v>
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.41e-08</v>
+        <v>1.4e-08</v>
       </c>
       <c r="F40" t="n">
         <v>0.87</v>
       </c>
       <c r="G40" t="n">
-        <v>0.555</v>
+        <v>0.556</v>
       </c>
       <c r="H40" t="n">
         <v>0.199</v>
@@ -2039,7 +2039,7 @@
         <v>0.204</v>
       </c>
       <c r="J40" t="n">
-        <v>8.46e-07</v>
+        <v>8.4e-07</v>
       </c>
     </row>
     <row r="41">
@@ -2070,7 +2070,7 @@
         <v>0.87</v>
       </c>
       <c r="G41" t="n">
-        <v>0.555</v>
+        <v>0.556</v>
       </c>
       <c r="H41" t="n">
         <v>0.199</v>
@@ -2199,7 +2199,7 @@
         <v>0.1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="45">
@@ -2279,7 +2279,7 @@
         <v>0.191</v>
       </c>
       <c r="J46" t="n">
-        <v>0.215</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="47">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0005240000000000001</v>
+        <v>0.000553</v>
       </c>
       <c r="F48" t="n">
         <v>0.779</v>
@@ -2356,10 +2356,10 @@
         <v>0.244</v>
       </c>
       <c r="I48" t="n">
-        <v>0.209</v>
+        <v>0.21</v>
       </c>
       <c r="J48" t="n">
-        <v>0.00242</v>
+        <v>0.00255</v>
       </c>
     </row>
     <row r="49">
@@ -2396,7 +2396,7 @@
         <v>0.244</v>
       </c>
       <c r="I49" t="n">
-        <v>0.209</v>
+        <v>0.21</v>
       </c>
       <c r="J49" t="n">
         <v>0.00184</v>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.00944</v>
+        <v>0.0098</v>
       </c>
       <c r="F50" t="n">
         <v>0.779</v>
       </c>
       <c r="G50" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="H50" t="n">
         <v>0.244</v>
@@ -2439,7 +2439,7 @@
         <v>0.202</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="51">
@@ -2470,7 +2470,7 @@
         <v>0.779</v>
       </c>
       <c r="G51" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="H51" t="n">
         <v>0.244</v>
@@ -2479,7 +2479,7 @@
         <v>0.202</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0268</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="52">
@@ -2519,7 +2519,7 @@
         <v>0.203</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0367</v>
+        <v>0.0356</v>
       </c>
     </row>
     <row r="53">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>8.61e-07</v>
+        <v>8.41e-07</v>
       </c>
       <c r="F58" t="n">
         <v>0.764</v>
@@ -2759,7 +2759,7 @@
         <v>0.229</v>
       </c>
       <c r="J58" t="n">
-        <v>1.29e-05</v>
+        <v>1.26e-05</v>
       </c>
     </row>
     <row r="59">
@@ -2824,22 +2824,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.51e-07</v>
+        <v>4.08e-07</v>
       </c>
       <c r="F60" t="n">
         <v>0.764</v>
       </c>
       <c r="G60" t="n">
-        <v>0.586</v>
+        <v>0.587</v>
       </c>
       <c r="H60" t="n">
         <v>0.26</v>
       </c>
       <c r="I60" t="n">
-        <v>0.229</v>
+        <v>0.23</v>
       </c>
       <c r="J60" t="n">
-        <v>9.02e-06</v>
+        <v>8.16e-06</v>
       </c>
     </row>
     <row r="61">
@@ -2870,13 +2870,13 @@
         <v>0.764</v>
       </c>
       <c r="G61" t="n">
-        <v>0.586</v>
+        <v>0.587</v>
       </c>
       <c r="H61" t="n">
         <v>0.26</v>
       </c>
       <c r="I61" t="n">
-        <v>0.229</v>
+        <v>0.23</v>
       </c>
       <c r="J61" t="n">
         <v>0.000458</v>
@@ -3144,22 +3144,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.192</v>
+        <v>0.158</v>
       </c>
       <c r="F68" t="n">
         <v>0.745</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H68" t="n">
         <v>0.193</v>
       </c>
       <c r="I68" t="n">
-        <v>0.199</v>
+        <v>0.195</v>
       </c>
       <c r="J68" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="69">
@@ -3184,22 +3184,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.198</v>
+        <v>0.14</v>
       </c>
       <c r="F69" t="n">
         <v>0.745</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H69" t="n">
         <v>0.193</v>
       </c>
       <c r="I69" t="n">
-        <v>0.199</v>
+        <v>0.195</v>
       </c>
       <c r="J69" t="n">
-        <v>0.258</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="70">
@@ -3224,22 +3224,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.107</v>
+        <v>0.0941</v>
       </c>
       <c r="F70" t="n">
         <v>0.745</v>
       </c>
       <c r="G70" t="n">
-        <v>0.839</v>
+        <v>0.841</v>
       </c>
       <c r="H70" t="n">
         <v>0.193</v>
       </c>
       <c r="I70" t="n">
-        <v>0.193</v>
+        <v>0.19</v>
       </c>
       <c r="J70" t="n">
-        <v>0.153</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="71">
@@ -3264,22 +3264,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0747</v>
       </c>
       <c r="F71" t="n">
         <v>0.745</v>
       </c>
       <c r="G71" t="n">
-        <v>0.839</v>
+        <v>0.841</v>
       </c>
       <c r="H71" t="n">
         <v>0.193</v>
       </c>
       <c r="I71" t="n">
-        <v>0.193</v>
+        <v>0.19</v>
       </c>
       <c r="J71" t="n">
-        <v>0.13</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="72">
@@ -3399,7 +3399,7 @@
         <v>0.163</v>
       </c>
       <c r="J74" t="n">
-        <v>0.215</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="75">
@@ -3439,7 +3439,7 @@
         <v>0.163</v>
       </c>
       <c r="J75" t="n">
-        <v>0.196</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="76">
@@ -3519,7 +3519,7 @@
         <v>0.124</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0273</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="78">
@@ -3544,22 +3544,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.455</v>
+        <v>0.414</v>
       </c>
       <c r="F78" t="n">
         <v>0.745</v>
       </c>
       <c r="G78" t="n">
-        <v>0.778</v>
+        <v>0.781</v>
       </c>
       <c r="H78" t="n">
         <v>0.166</v>
       </c>
       <c r="I78" t="n">
-        <v>0.182</v>
+        <v>0.18</v>
       </c>
       <c r="J78" t="n">
-        <v>0.506</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="79">
@@ -3584,22 +3584,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.211</v>
+        <v>0.173</v>
       </c>
       <c r="F79" t="n">
         <v>0.745</v>
       </c>
       <c r="G79" t="n">
-        <v>0.778</v>
+        <v>0.781</v>
       </c>
       <c r="H79" t="n">
         <v>0.166</v>
       </c>
       <c r="I79" t="n">
-        <v>0.182</v>
+        <v>0.18</v>
       </c>
       <c r="J79" t="n">
-        <v>0.264</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="80">
@@ -3624,22 +3624,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.249</v>
+        <v>0.221</v>
       </c>
       <c r="F80" t="n">
         <v>0.745</v>
       </c>
       <c r="G80" t="n">
-        <v>0.795</v>
+        <v>0.798</v>
       </c>
       <c r="H80" t="n">
         <v>0.166</v>
       </c>
       <c r="I80" t="n">
-        <v>0.176</v>
+        <v>0.173</v>
       </c>
       <c r="J80" t="n">
-        <v>0.318</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="81">
@@ -3670,16 +3670,16 @@
         <v>0.745</v>
       </c>
       <c r="G81" t="n">
-        <v>0.795</v>
+        <v>0.798</v>
       </c>
       <c r="H81" t="n">
         <v>0.166</v>
       </c>
       <c r="I81" t="n">
-        <v>0.176</v>
+        <v>0.173</v>
       </c>
       <c r="J81" t="n">
-        <v>0.258</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="82">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0245</v>
+        <v>0.0185</v>
       </c>
       <c r="F88" t="n">
         <v>0.696</v>
       </c>
       <c r="G88" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="H88" t="n">
         <v>0.181</v>
       </c>
       <c r="I88" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0445</v>
+        <v>0.0347</v>
       </c>
     </row>
     <row r="89">
@@ -3990,13 +3990,13 @@
         <v>0.696</v>
       </c>
       <c r="G89" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="H89" t="n">
         <v>0.181</v>
       </c>
       <c r="I89" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="J89" t="n">
         <v>0.0619</v>
@@ -4024,22 +4024,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.00726</v>
+        <v>0.0054</v>
       </c>
       <c r="F90" t="n">
         <v>0.696</v>
       </c>
       <c r="G90" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H90" t="n">
         <v>0.181</v>
       </c>
       <c r="I90" t="n">
-        <v>0.189</v>
+        <v>0.187</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0174</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="91">
@@ -4064,22 +4064,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.0268</v>
+        <v>0.0106</v>
       </c>
       <c r="F91" t="n">
         <v>0.696</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H91" t="n">
         <v>0.181</v>
       </c>
       <c r="I91" t="n">
-        <v>0.189</v>
+        <v>0.187</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0519</v>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="92">
@@ -4119,7 +4119,7 @@
         <v>0.118</v>
       </c>
       <c r="J92" t="n">
-        <v>0.00125</v>
+        <v>0.00121</v>
       </c>
     </row>
     <row r="93">
@@ -4344,13 +4344,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.000325</v>
+        <v>0.0003</v>
       </c>
       <c r="F98" t="n">
         <v>0.787</v>
       </c>
       <c r="G98" t="n">
-        <v>0.635</v>
+        <v>0.637</v>
       </c>
       <c r="H98" t="n">
         <v>0.165</v>
@@ -4359,7 +4359,7 @@
         <v>0.197</v>
       </c>
       <c r="J98" t="n">
-        <v>0.00177</v>
+        <v>0.00164</v>
       </c>
     </row>
     <row r="99">
@@ -4390,7 +4390,7 @@
         <v>0.787</v>
       </c>
       <c r="G99" t="n">
-        <v>0.635</v>
+        <v>0.637</v>
       </c>
       <c r="H99" t="n">
         <v>0.165</v>
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.000219</v>
+        <v>0.000201</v>
       </c>
       <c r="F100" t="n">
         <v>0.787</v>
       </c>
       <c r="G100" t="n">
-        <v>0.637</v>
+        <v>0.639</v>
       </c>
       <c r="H100" t="n">
         <v>0.165</v>
@@ -4439,7 +4439,7 @@
         <v>0.177</v>
       </c>
       <c r="J100" t="n">
-        <v>0.00131</v>
+        <v>0.00121</v>
       </c>
     </row>
     <row r="101">
@@ -4470,7 +4470,7 @@
         <v>0.787</v>
       </c>
       <c r="G101" t="n">
-        <v>0.637</v>
+        <v>0.639</v>
       </c>
       <c r="H101" t="n">
         <v>0.165</v>
@@ -4744,22 +4744,22 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.102</v>
+        <v>0.135</v>
       </c>
       <c r="F108" t="n">
         <v>0.741</v>
       </c>
       <c r="G108" t="n">
-        <v>0.709</v>
+        <v>0.711</v>
       </c>
       <c r="H108" t="n">
         <v>0.177</v>
       </c>
       <c r="I108" t="n">
-        <v>0.172</v>
+        <v>0.173</v>
       </c>
       <c r="J108" t="n">
-        <v>0.149</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="109">
@@ -4784,22 +4784,22 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.211</v>
+        <v>0.274</v>
       </c>
       <c r="F109" t="n">
         <v>0.741</v>
       </c>
       <c r="G109" t="n">
-        <v>0.709</v>
+        <v>0.711</v>
       </c>
       <c r="H109" t="n">
         <v>0.177</v>
       </c>
       <c r="I109" t="n">
-        <v>0.172</v>
+        <v>0.173</v>
       </c>
       <c r="J109" t="n">
-        <v>0.264</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="110">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.701</v>
+        <v>0.792</v>
       </c>
       <c r="F110" t="n">
         <v>0.741</v>
       </c>
       <c r="G110" t="n">
-        <v>0.734</v>
+        <v>0.736</v>
       </c>
       <c r="H110" t="n">
         <v>0.177</v>
@@ -4839,7 +4839,7 @@
         <v>0.171</v>
       </c>
       <c r="J110" t="n">
-        <v>0.738</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="111">
@@ -4864,13 +4864,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.744</v>
+        <v>0.706</v>
       </c>
       <c r="F111" t="n">
         <v>0.741</v>
       </c>
       <c r="G111" t="n">
-        <v>0.734</v>
+        <v>0.736</v>
       </c>
       <c r="H111" t="n">
         <v>0.177</v>
@@ -4879,7 +4879,7 @@
         <v>0.171</v>
       </c>
       <c r="J111" t="n">
-        <v>0.797</v>
+        <v>0.743</v>
       </c>
     </row>
     <row r="112">
@@ -4919,7 +4919,7 @@
         <v>0.183</v>
       </c>
       <c r="J112" t="n">
-        <v>0.506</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="113">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.0318</v>
+        <v>0.032</v>
       </c>
       <c r="F118" t="n">
         <v>0.709</v>
       </c>
       <c r="G118" t="n">
-        <v>0.655</v>
+        <v>0.656</v>
       </c>
       <c r="H118" t="n">
         <v>0.19</v>
@@ -5159,7 +5159,7 @@
         <v>0.199</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0561</v>
+        <v>0.0565</v>
       </c>
     </row>
     <row r="119">
@@ -5190,7 +5190,7 @@
         <v>0.709</v>
       </c>
       <c r="G119" t="n">
-        <v>0.655</v>
+        <v>0.656</v>
       </c>
       <c r="H119" t="n">
         <v>0.19</v>
@@ -5224,13 +5224,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.061</v>
+        <v>0.0626</v>
       </c>
       <c r="F120" t="n">
         <v>0.709</v>
       </c>
       <c r="G120" t="n">
-        <v>0.654</v>
+        <v>0.656</v>
       </c>
       <c r="H120" t="n">
         <v>0.19</v>
@@ -5239,7 +5239,7 @@
         <v>0.207</v>
       </c>
       <c r="J120" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0963</v>
       </c>
     </row>
     <row r="121">
@@ -5270,7 +5270,7 @@
         <v>0.709</v>
       </c>
       <c r="G121" t="n">
-        <v>0.654</v>
+        <v>0.656</v>
       </c>
       <c r="H121" t="n">
         <v>0.19</v>
@@ -5279,7 +5279,7 @@
         <v>0.207</v>
       </c>
       <c r="J121" t="n">
-        <v>0.128</v>
+        <v>0.125</v>
       </c>
     </row>
   </sheetData>
@@ -6894,7 +6894,7 @@
         <v>0.528</v>
       </c>
       <c r="I43" t="n">
-        <v>0.792</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="44">
@@ -9262,7 +9262,7 @@
         <v>0.762</v>
       </c>
       <c r="I107" t="n">
-        <v>0.85</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -11630,7 +11630,7 @@
         <v>0.601</v>
       </c>
       <c r="I171" t="n">
-        <v>0.82</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -12808,13 +12808,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G203" t="n">
-        <v>0.625</v>
+        <v>0.65</v>
       </c>
       <c r="H203" t="n">
-        <v>6.44e-09</v>
+        <v>5.85e-08</v>
       </c>
       <c r="I203" t="n">
-        <v>4.83e-08</v>
+        <v>4.39e-07</v>
       </c>
     </row>
     <row r="204">
@@ -13400,13 +13400,13 @@
         <v>0.981</v>
       </c>
       <c r="G219" t="n">
-        <v>0.623</v>
+        <v>0.643</v>
       </c>
       <c r="H219" t="n">
-        <v>2.77e-06</v>
+        <v>4.02e-06</v>
       </c>
       <c r="I219" t="n">
-        <v>2.08e-05</v>
+        <v>3.01e-05</v>
       </c>
     </row>
     <row r="220">
@@ -13992,13 +13992,13 @@
         <v>0.879</v>
       </c>
       <c r="G235" t="n">
-        <v>0.569</v>
+        <v>0.621</v>
       </c>
       <c r="H235" t="n">
-        <v>0.000323</v>
+        <v>0.00232</v>
       </c>
       <c r="I235" t="n">
-        <v>0.00242</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="236">
@@ -14584,13 +14584,13 @@
         <v>0.927</v>
       </c>
       <c r="G251" t="n">
-        <v>0.595</v>
+        <v>0.632</v>
       </c>
       <c r="H251" t="n">
-        <v>4.37e-09</v>
+        <v>5.84e-08</v>
       </c>
       <c r="I251" t="n">
-        <v>3.28e-08</v>
+        <v>4.38e-07</v>
       </c>
     </row>
     <row r="252">
@@ -15176,13 +15176,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G267" t="n">
-        <v>0.617</v>
+        <v>0.633</v>
       </c>
       <c r="H267" t="n">
-        <v>3.02e-09</v>
+        <v>1.36e-08</v>
       </c>
       <c r="I267" t="n">
-        <v>4.53e-08</v>
+        <v>2.04e-07</v>
       </c>
     </row>
     <row r="268">
@@ -15768,13 +15768,13 @@
         <v>0.981</v>
       </c>
       <c r="G283" t="n">
-        <v>0.611</v>
+        <v>0.625</v>
       </c>
       <c r="H283" t="n">
-        <v>1.25e-06</v>
+        <v>1.71e-06</v>
       </c>
       <c r="I283" t="n">
-        <v>1.88e-05</v>
+        <v>2.57e-05</v>
       </c>
     </row>
     <row r="284">
@@ -16360,13 +16360,13 @@
         <v>0.879</v>
       </c>
       <c r="G299" t="n">
-        <v>0.569</v>
+        <v>0.603</v>
       </c>
       <c r="H299" t="n">
-        <v>0.000323</v>
+        <v>0.00123</v>
       </c>
       <c r="I299" t="n">
-        <v>0.00242</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="300">
@@ -16952,13 +16952,13 @@
         <v>0.927</v>
       </c>
       <c r="G315" t="n">
-        <v>0.589</v>
+        <v>0.614</v>
       </c>
       <c r="H315" t="n">
-        <v>2.2e-09</v>
+        <v>1.35e-08</v>
       </c>
       <c r="I315" t="n">
-        <v>3.28e-08</v>
+        <v>2.02e-07</v>
       </c>
     </row>
     <row r="316">
@@ -24648,10 +24648,10 @@
         <v>0.792</v>
       </c>
       <c r="G523" t="n">
-        <v>0.783</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H523" t="n">
-        <v>1</v>
+        <v>0.872</v>
       </c>
       <c r="I523" t="n">
         <v>1</v>
@@ -25240,13 +25240,13 @@
         <v>0.971</v>
       </c>
       <c r="G539" t="n">
-        <v>0.9</v>
+        <v>0.907</v>
       </c>
       <c r="H539" t="n">
-        <v>0.364</v>
+        <v>0.372</v>
       </c>
       <c r="I539" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="540">
@@ -25832,13 +25832,13 @@
         <v>0.586</v>
       </c>
       <c r="G555" t="n">
-        <v>0.621</v>
+        <v>0.672</v>
       </c>
       <c r="H555" t="n">
-        <v>0.85</v>
+        <v>0.442</v>
       </c>
       <c r="I555" t="n">
-        <v>0.85</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="556">
@@ -26424,13 +26424,13 @@
         <v>0.731</v>
       </c>
       <c r="G571" t="n">
-        <v>0.735</v>
+        <v>0.772</v>
       </c>
       <c r="H571" t="n">
-        <v>1</v>
+        <v>0.618</v>
       </c>
       <c r="I571" t="n">
-        <v>1</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="572">
@@ -27016,10 +27016,10 @@
         <v>0.792</v>
       </c>
       <c r="G587" t="n">
-        <v>0.783</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H587" t="n">
-        <v>1</v>
+        <v>0.872</v>
       </c>
       <c r="I587" t="n">
         <v>1</v>
@@ -27608,13 +27608,13 @@
         <v>0.971</v>
       </c>
       <c r="G603" t="n">
-        <v>0.9</v>
+        <v>0.907</v>
       </c>
       <c r="H603" t="n">
-        <v>0.364</v>
+        <v>0.372</v>
       </c>
       <c r="I603" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="604">
@@ -28200,13 +28200,13 @@
         <v>0.586</v>
       </c>
       <c r="G619" t="n">
-        <v>0.621</v>
+        <v>0.672</v>
       </c>
       <c r="H619" t="n">
-        <v>0.85</v>
+        <v>0.442</v>
       </c>
       <c r="I619" t="n">
-        <v>0.85</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="620">
@@ -28792,13 +28792,13 @@
         <v>0.731</v>
       </c>
       <c r="G635" t="n">
-        <v>0.735</v>
+        <v>0.772</v>
       </c>
       <c r="H635" t="n">
-        <v>1</v>
+        <v>0.618</v>
       </c>
       <c r="I635" t="n">
-        <v>1</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="636">
@@ -33534,7 +33534,7 @@
         <v>0.00163</v>
       </c>
       <c r="I763" t="n">
-        <v>0.00489</v>
+        <v>0.00611</v>
       </c>
     </row>
     <row r="764">
@@ -35310,7 +35310,7 @@
         <v>0.819</v>
       </c>
       <c r="I811" t="n">
-        <v>0.85</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="812">
@@ -36488,13 +36488,13 @@
         <v>0.875</v>
       </c>
       <c r="G843" t="n">
-        <v>0.7</v>
+        <v>0.717</v>
       </c>
       <c r="H843" t="n">
-        <v>0.00144</v>
+        <v>0.00365</v>
       </c>
       <c r="I843" t="n">
-        <v>0.0054</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="844">
@@ -37080,13 +37080,13 @@
         <v>0.957</v>
       </c>
       <c r="G859" t="n">
-        <v>0.739</v>
+        <v>0.75</v>
       </c>
       <c r="H859" t="n">
-        <v>0.00363</v>
+        <v>0.00738</v>
       </c>
       <c r="I859" t="n">
-        <v>0.0136</v>
+        <v>0.0277</v>
       </c>
     </row>
     <row r="860">
@@ -37672,13 +37672,13 @@
         <v>0.776</v>
       </c>
       <c r="G875" t="n">
-        <v>0.586</v>
+        <v>0.621</v>
       </c>
       <c r="H875" t="n">
-        <v>0.0456</v>
+        <v>0.105</v>
       </c>
       <c r="I875" t="n">
-        <v>0.0977</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="876">
@@ -38264,13 +38264,13 @@
         <v>0.857</v>
       </c>
       <c r="G891" t="n">
-        <v>0.654</v>
+        <v>0.679</v>
       </c>
       <c r="H891" t="n">
-        <v>0.000695</v>
+        <v>0.00311</v>
       </c>
       <c r="I891" t="n">
-        <v>0.00261</v>
+        <v>0.00933</v>
       </c>
     </row>
     <row r="892">
@@ -38856,13 +38856,13 @@
         <v>0.875</v>
       </c>
       <c r="G907" t="n">
-        <v>0.667</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H907" t="n">
-        <v>0.00019</v>
+        <v>0.000537</v>
       </c>
       <c r="I907" t="n">
-        <v>0.00095</v>
+        <v>0.00269</v>
       </c>
     </row>
     <row r="908">
@@ -39448,13 +39448,13 @@
         <v>0.957</v>
       </c>
       <c r="G923" t="n">
-        <v>0.667</v>
+        <v>0.679</v>
       </c>
       <c r="H923" t="n">
-        <v>0.000282</v>
+        <v>0.000323</v>
       </c>
       <c r="I923" t="n">
-        <v>0.00141</v>
+        <v>0.00161</v>
       </c>
     </row>
     <row r="924">
@@ -40040,13 +40040,13 @@
         <v>0.776</v>
       </c>
       <c r="G939" t="n">
-        <v>0.621</v>
+        <v>0.655</v>
       </c>
       <c r="H939" t="n">
-        <v>0.105</v>
+        <v>0.217</v>
       </c>
       <c r="I939" t="n">
-        <v>0.197</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="940">
@@ -40632,13 +40632,13 @@
         <v>0.857</v>
       </c>
       <c r="G955" t="n">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="H955" t="n">
-        <v>0.000309</v>
+        <v>0.00145</v>
       </c>
       <c r="I955" t="n">
-        <v>0.00154</v>
+        <v>0.00611</v>
       </c>
     </row>
     <row r="956">
